--- a/data_lake/bart_temp_med/dt=2026-07-26/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-07-26/temperaturamed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D000F240-B532-4F05-9A13-06D58AB2D253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94B0A67-DCE3-4E23-AF83-63F37A42D43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Temperatura" sheetId="1" r:id="rId1"/>
@@ -6354,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="111" width="32.42578125" style="50" customWidth="1"/>
-    <col min="112" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="112" width="32.42578125" style="50" customWidth="1"/>
+    <col min="113" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6710,7 +6710,9 @@
       <c r="AH5" s="56">
         <v>27.8</v>
       </c>
-      <c r="AI5" s="56"/>
+      <c r="AI5" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AJ5" s="56"/>
       <c r="AK5" s="56"/>
       <c r="AL5" s="56"/>
@@ -6719,11 +6721,11 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.804166666666664</v>
+        <v>28.803999999999995</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6731,7 +6733,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.65095177769539347</v>
+        <v>0.65078511102872483</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6837,7 +6839,9 @@
       <c r="AH6" s="56">
         <v>27.5</v>
       </c>
-      <c r="AI6" s="56"/>
+      <c r="AI6" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AJ6" s="56"/>
       <c r="AK6" s="56"/>
       <c r="AL6" s="56"/>
@@ -6846,11 +6850,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.816666666666663</v>
+        <v>28.831999999999997</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6858,7 +6862,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.42143277771784327</v>
+        <v>0.43676611105117757</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6964,7 +6968,9 @@
       <c r="AH7" s="56">
         <v>28.8</v>
       </c>
-      <c r="AI7" s="56"/>
+      <c r="AI7" s="56">
+        <v>31</v>
+      </c>
       <c r="AJ7" s="56"/>
       <c r="AK7" s="56"/>
       <c r="AL7" s="56"/>
@@ -6973,11 +6979,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.462500000000002</v>
+        <v>31.444000000000003</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6985,7 +6991,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.2623195084485417</v>
+        <v>2.2438195084485422</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7091,7 +7097,9 @@
       <c r="AH8" s="56">
         <v>28.4</v>
       </c>
-      <c r="AI8" s="56"/>
+      <c r="AI8" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AJ8" s="56"/>
       <c r="AK8" s="56"/>
       <c r="AL8" s="56"/>
@@ -7100,11 +7108,11 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.720833333333335</v>
+        <v>29.712000000000003</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7112,7 +7120,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1422940171619338</v>
+        <v>1.1334606838286021</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7218,7 +7226,9 @@
       <c r="AH9" s="56">
         <v>28.7</v>
       </c>
-      <c r="AI9" s="56"/>
+      <c r="AI9" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AJ9" s="56"/>
       <c r="AK9" s="56"/>
       <c r="AL9" s="56"/>
@@ -7227,11 +7237,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.391666666666669</v>
+        <v>29.384000000000004</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7239,7 +7249,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.39580231596356086</v>
+        <v>-0.40346898263022624</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7345,7 +7355,9 @@
       <c r="AH10" s="56">
         <v>31.7</v>
       </c>
-      <c r="AI10" s="56"/>
+      <c r="AI10" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AJ10" s="56"/>
       <c r="AK10" s="56"/>
       <c r="AL10" s="56"/>
@@ -7354,11 +7366,11 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.733333333333334</v>
+        <v>31.684000000000001</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7366,7 +7378,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.6539112989282749</v>
+        <v>1.6045779655949417</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7472,7 +7484,9 @@
       <c r="AH11" s="56">
         <v>31.7</v>
       </c>
-      <c r="AI11" s="56"/>
+      <c r="AI11" s="56">
+        <v>33.200000000000003</v>
+      </c>
       <c r="AJ11" s="56"/>
       <c r="AK11" s="56"/>
       <c r="AL11" s="56"/>
@@ -7481,11 +7495,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.62916666666667</v>
+        <v>32.652000000000001</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7493,7 +7507,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>2.6252525894388192</v>
+        <v>2.6480859227721503</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7599,7 +7613,9 @@
       <c r="AH12" s="56">
         <v>29.2</v>
       </c>
-      <c r="AI12" s="56"/>
+      <c r="AI12" s="56">
+        <v>30.9</v>
+      </c>
       <c r="AJ12" s="56"/>
       <c r="AK12" s="56"/>
       <c r="AL12" s="56"/>
@@ -7608,11 +7624,11 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>30.083333333333329</v>
+        <v>30.115999999999996</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7620,7 +7636,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>1.8176669440177484</v>
+        <v>1.8503336106844159</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7726,7 +7742,9 @@
       <c r="AH13" s="56">
         <v>29.6</v>
       </c>
-      <c r="AI13" s="56"/>
+      <c r="AI13" s="56">
+        <v>30.3</v>
+      </c>
       <c r="AJ13" s="56"/>
       <c r="AK13" s="56"/>
       <c r="AL13" s="56"/>
@@ -7735,11 +7753,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>29.937499999999996</v>
+        <v>29.951999999999995</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7747,7 +7765,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.608105302187635</v>
+        <v>1.6226053021876332</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7853,7 +7871,9 @@
       <c r="AH14" s="56">
         <v>22.4</v>
       </c>
-      <c r="AI14" s="56"/>
+      <c r="AI14" s="56">
+        <v>23.1</v>
+      </c>
       <c r="AJ14" s="56"/>
       <c r="AK14" s="56"/>
       <c r="AL14" s="56"/>
@@ -7862,11 +7882,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.620833333333326</v>
+        <v>23.599999999999994</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7874,7 +7894,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.8992933094384767</v>
+        <v>1.8784599761051446</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7980,7 +8000,9 @@
       <c r="AH15" s="56">
         <v>31</v>
       </c>
-      <c r="AI15" s="56"/>
+      <c r="AI15" s="56">
+        <v>28.9</v>
+      </c>
       <c r="AJ15" s="56"/>
       <c r="AK15" s="56"/>
       <c r="AL15" s="56"/>
@@ -7989,11 +8011,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.170833333333334</v>
+        <v>29.16</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8001,7 +8023,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>0.93532795698925497</v>
+        <v>0.92449462365592083</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8107,7 +8129,9 @@
       <c r="AH16" s="56">
         <v>28.1</v>
       </c>
-      <c r="AI16" s="56"/>
+      <c r="AI16" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AJ16" s="56"/>
       <c r="AK16" s="56"/>
       <c r="AL16" s="56"/>
@@ -8116,11 +8140,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.337500000000002</v>
+        <v>28.388000000000002</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8128,7 +8152,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.69984715159702304</v>
+        <v>0.75034715159702259</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8234,7 +8258,9 @@
       <c r="AH17" s="56">
         <v>24.8</v>
       </c>
-      <c r="AI17" s="56"/>
+      <c r="AI17" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AJ17" s="56"/>
       <c r="AK17" s="56"/>
       <c r="AL17" s="56"/>
@@ -8243,11 +8269,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.675000000000001</v>
+        <v>24.692000000000004</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8255,7 +8281,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.69137633084380212</v>
+        <v>0.70837633084380514</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8361,7 +8387,9 @@
       <c r="AH18" s="56">
         <v>19.100000000000001</v>
       </c>
-      <c r="AI18" s="56"/>
+      <c r="AI18" s="56">
+        <v>18.899999999999999</v>
+      </c>
       <c r="AJ18" s="56"/>
       <c r="AK18" s="56"/>
       <c r="AL18" s="56"/>
@@ -8370,11 +8398,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.762500000000003</v>
+        <v>18.768000000000001</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8382,7 +8410,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.3441487455197212</v>
+        <v>1.349648745519719</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8488,7 +8516,9 @@
       <c r="AH19" s="56">
         <v>23</v>
       </c>
-      <c r="AI19" s="56"/>
+      <c r="AI19" s="56">
+        <v>23.3</v>
+      </c>
       <c r="AJ19" s="56"/>
       <c r="AK19" s="56"/>
       <c r="AL19" s="56"/>
@@ -8497,11 +8527,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.316666666666666</v>
+        <v>24.276</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8509,7 +8539,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.1831317204301151</v>
+        <v>2.1424650537634484</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8615,7 +8645,9 @@
       <c r="AH20" s="56">
         <v>25.4</v>
       </c>
-      <c r="AI20" s="56"/>
+      <c r="AI20" s="56">
+        <v>23.4</v>
+      </c>
       <c r="AJ20" s="56"/>
       <c r="AK20" s="56"/>
       <c r="AL20" s="56"/>
@@ -8624,11 +8656,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.320833333333329</v>
+        <v>24.283999999999995</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8636,7 +8668,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.7131679073614592</v>
+        <v>1.6763345740281252</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8742,7 +8774,9 @@
       <c r="AH21" s="56">
         <v>27.1</v>
       </c>
-      <c r="AI21" s="56"/>
+      <c r="AI21" s="56">
+        <v>26.8</v>
+      </c>
       <c r="AJ21" s="56"/>
       <c r="AK21" s="56"/>
       <c r="AL21" s="56"/>
@@ -8751,11 +8785,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.141666666666666</v>
+        <v>27.127999999999997</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8763,7 +8797,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.4515847749095343</v>
+        <v>2.4379181082428651</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8869,7 +8903,9 @@
       <c r="AH22" s="56">
         <v>16.100000000000001</v>
       </c>
-      <c r="AI22" s="56"/>
+      <c r="AI22" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AJ22" s="56"/>
       <c r="AK22" s="56"/>
       <c r="AL22" s="56"/>
@@ -8878,11 +8914,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.524999999999999</v>
+        <v>15.488</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8890,7 +8926,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.7446670802315989</v>
+        <v>1.7076670802315999</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8996,7 +9032,9 @@
       <c r="AH23" s="56">
         <v>26.1</v>
       </c>
-      <c r="AI23" s="56"/>
+      <c r="AI23" s="56">
+        <v>25.5</v>
+      </c>
       <c r="AJ23" s="56"/>
       <c r="AK23" s="56"/>
       <c r="AL23" s="56"/>
@@ -9005,11 +9043,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.141666666666662</v>
+        <v>26.115999999999996</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9123,7 +9161,9 @@
       <c r="AH24" s="56">
         <v>30.4</v>
       </c>
-      <c r="AI24" s="56"/>
+      <c r="AI24" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AJ24" s="56"/>
       <c r="AK24" s="56"/>
       <c r="AL24" s="56"/>
@@ -9132,11 +9172,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.400000000000006</v>
+        <v>29.408000000000005</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9144,7 +9184,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.0376415152638856</v>
+        <v>1.0456415152638847</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9250,7 +9290,9 @@
       <c r="AH25" s="56">
         <v>20.5</v>
       </c>
-      <c r="AI25" s="56"/>
+      <c r="AI25" s="56">
+        <v>22.6</v>
+      </c>
       <c r="AJ25" s="56"/>
       <c r="AK25" s="56"/>
       <c r="AL25" s="56"/>
@@ -9259,11 +9301,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>21.808333333333326</v>
+        <v>21.839999999999996</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9271,7 +9313,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.8749088771311264</v>
+        <v>1.9065755437977963</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9377,7 +9419,9 @@
       <c r="AH26" s="56">
         <v>10.1</v>
       </c>
-      <c r="AI26" s="56"/>
+      <c r="AI26" s="56">
+        <v>11.3</v>
+      </c>
       <c r="AJ26" s="56"/>
       <c r="AK26" s="56"/>
       <c r="AL26" s="56"/>
@@ -9386,11 +9430,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.616666666666665</v>
+        <v>11.603999999999999</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9398,7 +9442,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.2463517665130759</v>
+        <v>1.2336850998464097</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9504,7 +9548,9 @@
       <c r="AH27" s="56">
         <v>28.1</v>
       </c>
-      <c r="AI27" s="56"/>
+      <c r="AI27" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AJ27" s="56"/>
       <c r="AK27" s="56"/>
       <c r="AL27" s="56"/>
@@ -9513,11 +9559,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.054166666666671</v>
+        <v>28.112000000000002</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9525,7 +9571,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.0654606970708222</v>
+        <v>1.1232940304041534</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9631,7 +9677,9 @@
       <c r="AH28" s="56">
         <v>28.9</v>
       </c>
-      <c r="AI28" s="56"/>
+      <c r="AI28" s="56">
+        <v>25.3</v>
+      </c>
       <c r="AJ28" s="56"/>
       <c r="AK28" s="56"/>
       <c r="AL28" s="56"/>
@@ -9640,11 +9688,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.654166666666669</v>
+        <v>26.6</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9652,7 +9700,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.90274811518972697</v>
+        <v>0.84858144852305983</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9758,7 +9806,9 @@
       <c r="AH29" s="56">
         <v>28.4</v>
       </c>
-      <c r="AI29" s="56"/>
+      <c r="AI29" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AJ29" s="56"/>
       <c r="AK29" s="56"/>
       <c r="AL29" s="56"/>
@@ -9767,11 +9817,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.691666666666666</v>
+        <v>27.732000000000003</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9779,7 +9829,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.73762445240942753</v>
+        <v>0.77795778574276397</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9885,7 +9935,9 @@
       <c r="AH30" s="56">
         <v>27</v>
       </c>
-      <c r="AI30" s="56"/>
+      <c r="AI30" s="56">
+        <v>26</v>
+      </c>
       <c r="AJ30" s="56"/>
       <c r="AK30" s="56"/>
       <c r="AL30" s="56"/>
@@ -9894,11 +9946,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.233333333333334</v>
+        <v>25.263999999999999</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9906,7 +9958,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.71533185020396317</v>
+        <v>0.74599851687062824</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -10012,7 +10064,9 @@
       <c r="AH31" s="98">
         <v>25.2</v>
       </c>
-      <c r="AI31" s="98"/>
+      <c r="AI31" s="98">
+        <v>26.4</v>
+      </c>
       <c r="AJ31" s="98"/>
       <c r="AK31" s="98"/>
       <c r="AL31" s="98"/>
@@ -10021,11 +10075,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.845833333333331</v>
+        <v>26.827999999999996</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10033,7 +10087,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4768847072879332</v>
+        <v>1.4590513739545976</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10139,7 +10193,9 @@
       <c r="AH32" s="56">
         <v>20.333333333333329</v>
       </c>
-      <c r="AI32" s="56"/>
+      <c r="AI32" s="56">
+        <v>20.6</v>
+      </c>
       <c r="AJ32" s="56"/>
       <c r="AK32" s="56"/>
       <c r="AL32" s="56"/>
@@ -10148,11 +10204,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.537500000000001</v>
+        <v>20.54</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10160,7 +10216,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.8806439478911621</v>
+        <v>2.8831439478911598</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10266,7 +10322,9 @@
       <c r="AH33" s="56">
         <v>27.45</v>
       </c>
-      <c r="AI33" s="56"/>
+      <c r="AI33" s="56">
+        <v>29.2</v>
+      </c>
       <c r="AJ33" s="56"/>
       <c r="AK33" s="56"/>
       <c r="AL33" s="56"/>
@@ -10275,11 +10333,11 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>27.887500000000003</v>
+        <v>27.940000000000005</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10287,7 +10345,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.0600279187874513</v>
+        <v>1.1125279187874533</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10393,7 +10451,9 @@
       <c r="AH34" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="AI34" s="56"/>
+      <c r="AI34" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="AJ34" s="56"/>
       <c r="AK34" s="56"/>
       <c r="AL34" s="56"/>
@@ -10402,11 +10462,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.294444444444448</v>
+        <v>21.296000000000003</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10414,7 +10474,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.5072468527641263</v>
+        <v>1.5088024083196814</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10520,7 +10580,9 @@
       <c r="AH35" s="56">
         <v>23</v>
       </c>
-      <c r="AI35" s="56"/>
+      <c r="AI35" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AJ35" s="56"/>
       <c r="AK35" s="56"/>
       <c r="AL35" s="56"/>
@@ -10529,11 +10591,11 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.477083333333329</v>
+        <v>24.541999999999998</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10541,7 +10603,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.43883543361592814</v>
+        <v>0.50375210028259687</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10647,7 +10709,9 @@
       <c r="AH36" s="56">
         <v>19</v>
       </c>
-      <c r="AI36" s="56"/>
+      <c r="AI36" s="56">
+        <v>19.55</v>
+      </c>
       <c r="AJ36" s="56"/>
       <c r="AK36" s="56"/>
       <c r="AL36" s="56"/>
@@ -10656,11 +10720,11 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>20.060416666666669</v>
+        <v>20.040000000000003</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10668,7 +10732,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.0616056034482781</v>
+        <v>1.0411889367816123</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10774,7 +10838,9 @@
       <c r="AH37" s="56">
         <v>27.45</v>
       </c>
-      <c r="AI37" s="56"/>
+      <c r="AI37" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AJ37" s="56"/>
       <c r="AK37" s="56"/>
       <c r="AL37" s="56"/>
@@ -10783,11 +10849,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.393750000000008</v>
+        <v>27.394000000000005</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10795,7 +10861,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.5075201260626265</v>
+        <v>1.5077701260626242</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10897,7 +10963,9 @@
       <c r="AH38" s="56">
         <v>16.3</v>
       </c>
-      <c r="AI38" s="56"/>
+      <c r="AI38" s="56">
+        <v>15.2</v>
+      </c>
       <c r="AJ38" s="56"/>
       <c r="AK38" s="56"/>
       <c r="AL38" s="56"/>
@@ -10906,11 +10974,11 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>16.009090909090908</v>
+        <v>15.973913043478261</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10918,7 +10986,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>0.99116190214022737</v>
+        <v>0.95598403652758002</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11022,7 +11090,9 @@
       <c r="AH39" s="56">
         <v>21.86666666666666</v>
       </c>
-      <c r="AI39" s="56"/>
+      <c r="AI39" s="56">
+        <v>21.8</v>
+      </c>
       <c r="AJ39" s="56"/>
       <c r="AK39" s="56"/>
       <c r="AL39" s="56"/>
@@ -11031,11 +11101,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.350724637681161</v>
+        <v>22.327777777777779</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11134,8 +11204,12 @@
         <v>25.15</v>
       </c>
       <c r="AG40" s="56"/>
-      <c r="AH40" s="56"/>
-      <c r="AI40" s="56"/>
+      <c r="AH40" s="56">
+        <v>24.333333333333329</v>
+      </c>
+      <c r="AI40" s="56">
+        <v>24.13333333333334</v>
+      </c>
       <c r="AJ40" s="56"/>
       <c r="AK40" s="56"/>
       <c r="AL40" s="56"/>
@@ -11144,11 +11218,11 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.444117647058821</v>
+        <v>25.316666666666663</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11156,7 +11230,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.5923268986318497</v>
+        <v>2.4648759182396915</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11260,7 +11334,9 @@
       <c r="AH41" s="56">
         <v>18</v>
       </c>
-      <c r="AI41" s="56"/>
+      <c r="AI41" s="56">
+        <v>20.466666666666669</v>
+      </c>
       <c r="AJ41" s="56"/>
       <c r="AK41" s="56"/>
       <c r="AL41" s="56"/>
@@ -11269,11 +11345,11 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.175362318840577</v>
+        <v>20.187499999999996</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11281,7 +11357,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>1.6832531275128382</v>
+        <v>1.6953908086722578</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11387,7 +11463,9 @@
       <c r="AH42" s="56">
         <v>27.5</v>
       </c>
-      <c r="AI42" s="56"/>
+      <c r="AI42" s="56">
+        <v>28.55</v>
+      </c>
       <c r="AJ42" s="56"/>
       <c r="AK42" s="56"/>
       <c r="AL42" s="56"/>
@@ -11396,11 +11474,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.998958333333334</v>
+        <v>28.021000000000001</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11408,7 +11486,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.24627281627506292</v>
+        <v>0.26831448294172944</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11510,7 +11588,9 @@
       <c r="AH43" s="56">
         <v>28.6</v>
       </c>
-      <c r="AI43" s="56"/>
+      <c r="AI43" s="56">
+        <v>29.75</v>
+      </c>
       <c r="AJ43" s="56"/>
       <c r="AK43" s="56"/>
       <c r="AL43" s="56"/>
@@ -11519,11 +11599,11 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.356818181818188</v>
+        <v>29.373913043478268</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11637,7 +11717,9 @@
       <c r="AH44" s="56">
         <v>28.9</v>
       </c>
-      <c r="AI44" s="56"/>
+      <c r="AI44" s="56">
+        <v>28.95</v>
+      </c>
       <c r="AJ44" s="56"/>
       <c r="AK44" s="56"/>
       <c r="AL44" s="56"/>
@@ -11646,11 +11728,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.486458333333328</v>
+        <v>28.504999999999995</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11658,7 +11740,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.1441148890505062</v>
+        <v>1.1626565557171737</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11764,7 +11846,9 @@
       <c r="AH45" s="56">
         <v>28.45</v>
       </c>
-      <c r="AI45" s="56"/>
+      <c r="AI45" s="56">
+        <v>29.65</v>
+      </c>
       <c r="AJ45" s="56"/>
       <c r="AK45" s="56"/>
       <c r="AL45" s="56"/>
@@ -11773,11 +11857,11 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.285416666666674</v>
+        <v>29.300000000000004</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11785,7 +11869,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.5173091917352437</v>
+        <v>1.5318925250685744</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11891,7 +11975,9 @@
       <c r="AH46" s="56">
         <v>29.3</v>
       </c>
-      <c r="AI46" s="56"/>
+      <c r="AI46" s="56">
+        <v>29.4</v>
+      </c>
       <c r="AJ46" s="56"/>
       <c r="AK46" s="56"/>
       <c r="AL46" s="56"/>
@@ -11900,11 +11986,11 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>28.944791666666664</v>
+        <v>28.962999999999997</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11912,7 +11998,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>1.0385940347691829</v>
+        <v>1.0568023681025167</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12018,7 +12104,9 @@
       <c r="AH47" s="56">
         <v>29.333333333333329</v>
       </c>
-      <c r="AI47" s="56"/>
+      <c r="AI47" s="56">
+        <v>31.4</v>
+      </c>
       <c r="AJ47" s="56"/>
       <c r="AK47" s="56"/>
       <c r="AL47" s="56"/>
@@ -12027,11 +12115,11 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ47" s="71">
         <f t="shared" si="1"/>
-        <v>29.94861111111112</v>
+        <v>30.006666666666675</v>
       </c>
       <c r="AR47" s="71">
         <f>IFERROR(VLOOKUP(A47,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12039,7 +12127,7 @@
       </c>
       <c r="AS47" s="71">
         <f t="shared" si="2"/>
-        <v>1.9797352517937306</v>
+        <v>2.0377908073492854</v>
       </c>
     </row>
     <row r="48" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12303,7 +12391,9 @@
       <c r="AH50" s="56">
         <v>28.35</v>
       </c>
-      <c r="AI50" s="56"/>
+      <c r="AI50" s="56">
+        <v>29.05</v>
+      </c>
       <c r="AJ50" s="56"/>
       <c r="AK50" s="56"/>
       <c r="AL50" s="56"/>
@@ -12312,11 +12402,11 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>29.28125</v>
+        <v>29.271999999999998</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12324,7 +12414,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>1.9925596539681791</v>
+        <v>1.9833096539681776</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12616,7 +12706,9 @@
       <c r="AH53" s="56">
         <v>27.65</v>
       </c>
-      <c r="AI53" s="56"/>
+      <c r="AI53" s="56">
+        <v>29</v>
+      </c>
       <c r="AJ53" s="56"/>
       <c r="AK53" s="56"/>
       <c r="AL53" s="56"/>
@@ -12625,11 +12717,11 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>28.933333333333334</v>
+        <v>28.936</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12637,7 +12729,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.5740870367427853</v>
+        <v>1.5767537034094516</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12743,7 +12835,9 @@
       <c r="AH54" s="56">
         <v>29.45</v>
       </c>
-      <c r="AI54" s="56"/>
+      <c r="AI54" s="56">
+        <v>30.45</v>
+      </c>
       <c r="AJ54" s="56"/>
       <c r="AK54" s="56"/>
       <c r="AL54" s="56"/>
@@ -12752,11 +12846,11 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>30.125000000000004</v>
+        <v>30.138000000000005</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12764,7 +12858,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.6267739749335846</v>
+        <v>1.6397739749335862</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12856,7 +12950,9 @@
       <c r="AH55" s="56">
         <v>29.35</v>
       </c>
-      <c r="AI55" s="56"/>
+      <c r="AI55" s="56">
+        <v>28.95</v>
+      </c>
       <c r="AJ55" s="56"/>
       <c r="AK55" s="56"/>
       <c r="AL55" s="56"/>
@@ -12865,11 +12961,11 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v>30.397058823529413</v>
+        <v>30.31666666666667</v>
       </c>
       <c r="AR55" s="71">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12877,7 +12973,7 @@
       </c>
       <c r="AS55" s="71">
         <f t="shared" si="2"/>
-        <v>1.9660991532923724</v>
+        <v>1.8857069964296294</v>
       </c>
     </row>
     <row r="56" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12983,7 +13079,9 @@
       <c r="AH56" s="56">
         <v>27.8</v>
       </c>
-      <c r="AI56" s="56"/>
+      <c r="AI56" s="56">
+        <v>27.45</v>
+      </c>
       <c r="AJ56" s="56"/>
       <c r="AK56" s="56"/>
       <c r="AL56" s="56"/>
@@ -12992,11 +13090,11 @@
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ56" s="71">
         <f t="shared" si="1"/>
-        <v>29.549999999999997</v>
+        <v>29.465999999999998</v>
       </c>
       <c r="AR56" s="71" t="str">
         <f>IFERROR(VLOOKUP(A56,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13266,7 +13364,9 @@
       <c r="AH59" s="56">
         <v>26.65</v>
       </c>
-      <c r="AI59" s="56"/>
+      <c r="AI59" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AJ59" s="56"/>
       <c r="AK59" s="56"/>
       <c r="AL59" s="56"/>
@@ -13275,11 +13375,11 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>29.116304347826084</v>
+        <v>29.098958333333332</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13287,7 +13387,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>1.0020845187439242</v>
+        <v>0.98473850425117249</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13508,7 +13608,9 @@
       <c r="AH61" s="56">
         <v>27.25</v>
       </c>
-      <c r="AI61" s="56"/>
+      <c r="AI61" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AJ61" s="56"/>
       <c r="AK61" s="56"/>
       <c r="AL61" s="56"/>
@@ -13517,11 +13619,11 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>26.629166666666674</v>
+        <v>26.668000000000006</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13529,7 +13631,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>0.92249498494071247</v>
+        <v>0.9613283182740453</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13902,7 +14004,9 @@
       <c r="AH65" s="56">
         <v>26.7</v>
       </c>
-      <c r="AI65" s="56"/>
+      <c r="AI65" s="56">
+        <v>25.3</v>
+      </c>
       <c r="AJ65" s="56"/>
       <c r="AK65" s="56"/>
       <c r="AL65" s="56"/>
@@ -13911,11 +14015,11 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>25.806666666666672</v>
+        <v>25.775000000000006</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13923,7 +14027,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.80146070835551342</v>
+        <v>0.76979404168884713</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14029,7 +14133,9 @@
       <c r="AH66" s="56">
         <v>27.55</v>
       </c>
-      <c r="AI66" s="56"/>
+      <c r="AI66" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AJ66" s="56"/>
       <c r="AK66" s="56"/>
       <c r="AL66" s="56"/>
@@ -14038,11 +14144,11 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.620833333333326</v>
+        <v>25.647999999999993</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14050,7 +14156,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.71171850305433537</v>
+        <v>0.73888516972100149</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14152,7 +14258,9 @@
       <c r="AH67" s="56">
         <v>27.85</v>
       </c>
-      <c r="AI67" s="56"/>
+      <c r="AI67" s="56">
+        <v>25.9</v>
+      </c>
       <c r="AJ67" s="56"/>
       <c r="AK67" s="56"/>
       <c r="AL67" s="56"/>
@@ -14161,11 +14269,11 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.447727272727274</v>
+        <v>25.467391304347824</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14173,7 +14281,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.79652036089606426</v>
+        <v>0.81618439251661457</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14279,7 +14387,9 @@
       <c r="AH68" s="56">
         <v>26.05</v>
       </c>
-      <c r="AI68" s="56"/>
+      <c r="AI68" s="56">
+        <v>24.75</v>
+      </c>
       <c r="AJ68" s="56"/>
       <c r="AK68" s="56"/>
       <c r="AL68" s="56"/>
@@ -14288,11 +14398,11 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.477083333333329</v>
+        <v>25.447999999999997</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14300,7 +14410,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>0.95199583059030957</v>
+        <v>0.9229124972569771</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14406,7 +14516,9 @@
       <c r="AH69" s="56">
         <v>26.45</v>
       </c>
-      <c r="AI69" s="56"/>
+      <c r="AI69" s="56">
+        <v>25.35</v>
+      </c>
       <c r="AJ69" s="56"/>
       <c r="AK69" s="56"/>
       <c r="AL69" s="56"/>
@@ -14415,11 +14527,11 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>24.939583333333335</v>
+        <v>24.956000000000003</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14427,7 +14539,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.61718564670132636</v>
+        <v>0.63360231336799444</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14519,7 +14631,9 @@
       <c r="AH70" s="56">
         <v>26.766666666666669</v>
       </c>
-      <c r="AI70" s="56"/>
+      <c r="AI70" s="56">
+        <v>27.466666666666669</v>
+      </c>
       <c r="AJ70" s="56"/>
       <c r="AK70" s="56"/>
       <c r="AL70" s="56"/>
@@ -14528,11 +14642,11 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>26.441176470588236</v>
+        <v>26.49814814814815</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14540,7 +14654,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>0.87121777954503443</v>
+        <v>0.92818945710494916</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14646,7 +14760,9 @@
       <c r="AH71" s="56">
         <v>26.766666666666669</v>
       </c>
-      <c r="AI71" s="56"/>
+      <c r="AI71" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AJ71" s="56"/>
       <c r="AK71" s="56"/>
       <c r="AL71" s="56"/>
@@ -14655,11 +14771,11 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.938888888888886</v>
+        <v>25.945333333333334</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14667,7 +14783,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.27644597523535808</v>
+        <v>0.28289041967980566</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14771,7 +14887,9 @@
       <c r="AH72" s="56">
         <v>25.966666666666669</v>
       </c>
-      <c r="AI72" s="56"/>
+      <c r="AI72" s="56">
+        <v>25.9</v>
+      </c>
       <c r="AJ72" s="56"/>
       <c r="AK72" s="56"/>
       <c r="AL72" s="56"/>
@@ -14780,11 +14898,11 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>25.4304347826087</v>
+        <v>25.450000000000003</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14792,7 +14910,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.45722603964916075</v>
+        <v>0.47679125704046399</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15013,7 +15131,9 @@
       <c r="AH74" s="56">
         <v>22.2</v>
       </c>
-      <c r="AI74" s="56"/>
+      <c r="AI74" s="56">
+        <v>22.25</v>
+      </c>
       <c r="AJ74" s="56"/>
       <c r="AK74" s="56"/>
       <c r="AL74" s="56"/>
@@ -15022,11 +15142,11 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>20.737500000000001</v>
+        <v>20.798000000000002</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15034,7 +15154,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.73900125063989108</v>
+        <v>0.79950125063989219</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15140,7 +15260,9 @@
       <c r="AH75" s="56">
         <v>16.13333333333334</v>
       </c>
-      <c r="AI75" s="56"/>
+      <c r="AI75" s="56">
+        <v>16.333333333333329</v>
+      </c>
       <c r="AJ75" s="56"/>
       <c r="AK75" s="56"/>
       <c r="AL75" s="56"/>
@@ -15149,11 +15271,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>15.865277777777772</v>
+        <v>15.883999999999993</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15161,7 +15283,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.68423408581098144</v>
+        <v>0.70295630803320286</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15267,7 +15389,9 @@
       <c r="AH76" s="56">
         <v>21.1</v>
       </c>
-      <c r="AI76" s="56"/>
+      <c r="AI76" s="56">
+        <v>20.6</v>
+      </c>
       <c r="AJ76" s="56"/>
       <c r="AK76" s="56"/>
       <c r="AL76" s="56"/>
@@ -15276,11 +15400,11 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>20.744791666666668</v>
+        <v>20.739000000000001</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15288,7 +15412,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>0.94482505514044846</v>
+        <v>0.93903338847378137</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15394,7 +15518,9 @@
       <c r="AH77" s="56">
         <v>24.8</v>
       </c>
-      <c r="AI77" s="56"/>
+      <c r="AI77" s="56">
+        <v>23.533333333333331</v>
+      </c>
       <c r="AJ77" s="56"/>
       <c r="AK77" s="56"/>
       <c r="AL77" s="56"/>
@@ -15403,11 +15529,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>23.927777777777774</v>
+        <v>23.911999999999992</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15415,7 +15541,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.2445369217988542</v>
+        <v>1.2287591440210726</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15521,7 +15647,9 @@
       <c r="AH78" s="56">
         <v>32.25</v>
       </c>
-      <c r="AI78" s="56"/>
+      <c r="AI78" s="56">
+        <v>31.1</v>
+      </c>
       <c r="AJ78" s="56"/>
       <c r="AK78" s="56"/>
       <c r="AL78" s="56"/>
@@ -15530,11 +15658,11 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>31.133333333333329</v>
+        <v>31.131999999999998</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15542,7 +15670,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>1.9494035228106803</v>
+        <v>1.9480701894773489</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15644,7 +15772,9 @@
       <c r="AH79" s="56">
         <v>32.133333333333333</v>
       </c>
-      <c r="AI79" s="56"/>
+      <c r="AI79" s="56">
+        <v>31.4</v>
+      </c>
       <c r="AJ79" s="56"/>
       <c r="AK79" s="56"/>
       <c r="AL79" s="56"/>
@@ -15653,11 +15783,11 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.181818181818176</v>
+        <v>31.19130434782608</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15665,7 +15795,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>1.7127652973674472</v>
+        <v>1.7222514633753505</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15759,11 +15889,21 @@
       <c r="AD80" s="56">
         <v>22.2</v>
       </c>
-      <c r="AE80" s="56"/>
-      <c r="AF80" s="56"/>
-      <c r="AG80" s="56"/>
-      <c r="AH80" s="56"/>
-      <c r="AI80" s="56"/>
+      <c r="AE80" s="56">
+        <v>21.933333333333341</v>
+      </c>
+      <c r="AF80" s="56">
+        <v>22.06666666666667</v>
+      </c>
+      <c r="AG80" s="56">
+        <v>20.733333333333331</v>
+      </c>
+      <c r="AH80" s="56">
+        <v>22</v>
+      </c>
+      <c r="AI80" s="56">
+        <v>20</v>
+      </c>
       <c r="AJ80" s="56"/>
       <c r="AK80" s="56"/>
       <c r="AL80" s="56"/>
@@ -15772,11 +15912,11 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AQ80" s="71">
         <f t="shared" si="4"/>
-        <v>20.646666666666665</v>
+        <v>20.786666666666665</v>
       </c>
       <c r="AR80" s="71">
         <f>IFERROR(VLOOKUP(A80,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15784,7 +15924,7 @@
       </c>
       <c r="AS80" s="71">
         <f t="shared" si="5"/>
-        <v>1.3400872377361459</v>
+        <v>1.4800872377361465</v>
       </c>
     </row>
     <row r="81" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15884,7 +16024,9 @@
       <c r="AH81" s="56">
         <v>24.1</v>
       </c>
-      <c r="AI81" s="56"/>
+      <c r="AI81" s="56">
+        <v>25.85</v>
+      </c>
       <c r="AJ81" s="56"/>
       <c r="AK81" s="56"/>
       <c r="AL81" s="56"/>
@@ -15893,11 +16035,11 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v>23.976190476190474</v>
+        <v>24.061363636363634</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15905,7 +16047,7 @@
       </c>
       <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v>-0.19843942990129548</v>
+        <v>-0.11326626972813614</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16011,7 +16153,9 @@
       <c r="AH82" s="56">
         <v>26.933333333333341</v>
       </c>
-      <c r="AI82" s="56"/>
+      <c r="AI82" s="56">
+        <v>27.13333333333334</v>
+      </c>
       <c r="AJ82" s="56"/>
       <c r="AK82" s="56"/>
       <c r="AL82" s="56"/>
@@ -16020,11 +16164,11 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>26.081944444444446</v>
+        <v>26.124000000000002</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16032,7 +16176,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>0.90822198702286627</v>
+        <v>0.9502775425784229</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16278,7 +16422,9 @@
       <c r="AH85" s="56">
         <v>30.65</v>
       </c>
-      <c r="AI85" s="56"/>
+      <c r="AI85" s="56">
+        <v>30.7</v>
+      </c>
       <c r="AJ85" s="56"/>
       <c r="AK85" s="56"/>
       <c r="AL85" s="56"/>
@@ -16287,11 +16433,11 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>30.883333333333333</v>
+        <v>30.871874999999999</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16405,7 +16551,9 @@
       <c r="AH86" s="56">
         <v>29.8</v>
       </c>
-      <c r="AI86" s="56"/>
+      <c r="AI86" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AJ86" s="56"/>
       <c r="AK86" s="56"/>
       <c r="AL86" s="56"/>
@@ -16414,11 +16562,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.756249999999994</v>
+        <v>29.749999999999996</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16426,7 +16574,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.1441668384452051</v>
+        <v>1.1379168384452072</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16532,7 +16680,9 @@
       <c r="AH87" s="56">
         <v>30.9</v>
       </c>
-      <c r="AI87" s="56"/>
+      <c r="AI87" s="56">
+        <v>30.85</v>
+      </c>
       <c r="AJ87" s="56"/>
       <c r="AK87" s="56"/>
       <c r="AL87" s="56"/>
@@ -16541,11 +16691,11 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>31.872916666666669</v>
+        <v>31.832000000000004</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16553,7 +16703,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>2.8667266942042779</v>
+        <v>2.8258100275376137</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16659,7 +16809,9 @@
       <c r="AH88" s="56">
         <v>29.35</v>
       </c>
-      <c r="AI88" s="56"/>
+      <c r="AI88" s="56">
+        <v>31.75</v>
+      </c>
       <c r="AJ88" s="56"/>
       <c r="AK88" s="56"/>
       <c r="AL88" s="56"/>
@@ -16668,11 +16820,11 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.125000000000004</v>
+        <v>30.190000000000005</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16680,7 +16832,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>1.4341253840245933</v>
+        <v>1.4991253840245946</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16774,7 +16926,9 @@
       <c r="AH89" s="56">
         <v>31.5</v>
       </c>
-      <c r="AI89" s="56"/>
+      <c r="AI89" s="56">
+        <v>34.700000000000003</v>
+      </c>
       <c r="AJ89" s="56"/>
       <c r="AK89" s="56"/>
       <c r="AL89" s="56"/>
@@ -16783,11 +16937,11 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>33.413888888888884</v>
+        <v>33.481578947368419</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16795,7 +16949,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>3.9313898472421833</v>
+        <v>3.9990799057217181</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16893,7 +17047,9 @@
       <c r="AH90" s="56">
         <v>30.7</v>
       </c>
-      <c r="AI90" s="56"/>
+      <c r="AI90" s="56">
+        <v>31.85</v>
+      </c>
       <c r="AJ90" s="56"/>
       <c r="AK90" s="56"/>
       <c r="AL90" s="56"/>
@@ -16902,11 +17058,11 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>32.125</v>
+        <v>32.111904761904761</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16914,7 +17070,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>3.0899399420873408</v>
+        <v>3.0768447039921014</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17135,7 +17291,9 @@
       <c r="AH92" s="56">
         <v>17.25</v>
       </c>
-      <c r="AI92" s="56"/>
+      <c r="AI92" s="56">
+        <v>17.25</v>
+      </c>
       <c r="AJ92" s="56"/>
       <c r="AK92" s="56"/>
       <c r="AL92" s="56"/>
@@ -17144,11 +17302,11 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.576388888888893</v>
+        <v>17.563333333333336</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17156,7 +17314,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.4130448028674216</v>
+        <v>1.3999892473118649</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17262,7 +17420,9 @@
       <c r="AH93" s="56">
         <v>23.733333333333331</v>
       </c>
-      <c r="AI93" s="56"/>
+      <c r="AI93" s="56">
+        <v>23.4</v>
+      </c>
       <c r="AJ93" s="56"/>
       <c r="AK93" s="56"/>
       <c r="AL93" s="56"/>
@@ -17271,11 +17431,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.630555555555556</v>
+        <v>23.621333333333332</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17283,7 +17443,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.5210676896859354</v>
+        <v>1.5118454674637114</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17386,8 +17546,12 @@
       <c r="AG94" s="56">
         <v>16.8</v>
       </c>
-      <c r="AH94" s="56"/>
-      <c r="AI94" s="56"/>
+      <c r="AH94" s="56">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="AI94" s="56">
+        <v>16.850000000000001</v>
+      </c>
       <c r="AJ94" s="56"/>
       <c r="AK94" s="56"/>
       <c r="AL94" s="56"/>
@@ -17396,11 +17560,11 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.34021739130435</v>
+        <v>17.313000000000002</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17408,7 +17572,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.244990245369781</v>
+        <v>1.2177728540654336</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17514,7 +17678,9 @@
       <c r="AH95" s="56">
         <v>14.65</v>
       </c>
-      <c r="AI95" s="56"/>
+      <c r="AI95" s="56">
+        <v>15.4</v>
+      </c>
       <c r="AJ95" s="56"/>
       <c r="AK95" s="56"/>
       <c r="AL95" s="56"/>
@@ -17523,11 +17689,11 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.660416666666668</v>
+        <v>14.69</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17535,7 +17701,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.0276085305148079</v>
+        <v>1.0571918638481392</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17799,7 +17965,9 @@
       <c r="AH98" s="56">
         <v>12.25</v>
       </c>
-      <c r="AI98" s="56"/>
+      <c r="AI98" s="56">
+        <v>12.75</v>
+      </c>
       <c r="AJ98" s="56"/>
       <c r="AK98" s="56"/>
       <c r="AL98" s="56"/>
@@ -17808,11 +17976,11 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.189583333333333</v>
+        <v>13.172000000000001</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17922,7 +18090,9 @@
       <c r="AH99" s="56">
         <v>14.16666666666667</v>
       </c>
-      <c r="AI99" s="56"/>
+      <c r="AI99" s="56">
+        <v>15.866666666666671</v>
+      </c>
       <c r="AJ99" s="56"/>
       <c r="AK99" s="56"/>
       <c r="AL99" s="56"/>
@@ -17931,11 +18101,11 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.41818181818182</v>
+        <v>14.481159420289858</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18277,7 +18447,9 @@
       <c r="AH102" s="56">
         <v>11.93333333333333</v>
       </c>
-      <c r="AI102" s="56"/>
+      <c r="AI102" s="56">
+        <v>12.733333333333331</v>
+      </c>
       <c r="AJ102" s="56"/>
       <c r="AK102" s="56"/>
       <c r="AL102" s="56"/>
@@ -18286,11 +18458,11 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>13.050793650793654</v>
+        <v>13.036363636363639</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18298,7 +18470,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>1.8037982814077633</v>
+        <v>1.789368266977748</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18556,7 +18728,9 @@
       <c r="AH105" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="AI105" s="56"/>
+      <c r="AI105" s="56">
+        <v>17.866666666666671</v>
+      </c>
       <c r="AJ105" s="56"/>
       <c r="AK105" s="56"/>
       <c r="AL105" s="56"/>
@@ -18565,11 +18739,11 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.142857142857142</v>
+        <v>18.130303030303029</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18577,7 +18751,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.0983196343808714</v>
+        <v>1.0857655218267581</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18867,9 +19041,11 @@
         <v>14.85</v>
       </c>
       <c r="AH108" s="56">
-        <v>10.65</v>
-      </c>
-      <c r="AI108" s="56"/>
+        <v>15.65</v>
+      </c>
+      <c r="AI108" s="56">
+        <v>16.25</v>
+      </c>
       <c r="AJ108" s="56"/>
       <c r="AK108" s="56"/>
       <c r="AL108" s="56"/>
@@ -18878,11 +19054,11 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>13.954166666666667</v>
+        <v>14.246000000000002</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18890,7 +19066,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>-0.27486624806514293</v>
+        <v>1.6967085268191795E-2</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18996,7 +19172,9 @@
       <c r="AH109" s="56">
         <v>14.6</v>
       </c>
-      <c r="AI109" s="56"/>
+      <c r="AI109" s="56">
+        <v>15.7</v>
+      </c>
       <c r="AJ109" s="56"/>
       <c r="AK109" s="56"/>
       <c r="AL109" s="56"/>
@@ -19005,11 +19183,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.514583333333333</v>
+        <v>14.561999999999998</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19017,7 +19195,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.8008202458255429</v>
+        <v>0.84823691249220801</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19123,7 +19301,9 @@
       <c r="AH110" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="AI110" s="56"/>
+      <c r="AI110" s="56">
+        <v>18.266666666666669</v>
+      </c>
       <c r="AJ110" s="56"/>
       <c r="AK110" s="56"/>
       <c r="AL110" s="56"/>
@@ -19132,11 +19312,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.463888888888885</v>
+        <v>17.495999999999995</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19144,7 +19324,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.52892685042199616</v>
+        <v>0.56103796153310626</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19250,7 +19430,9 @@
       <c r="AH111" s="56">
         <v>16.06666666666667</v>
       </c>
-      <c r="AI111" s="56"/>
+      <c r="AI111" s="56">
+        <v>16.666666666666671</v>
+      </c>
       <c r="AJ111" s="56"/>
       <c r="AK111" s="56"/>
       <c r="AL111" s="56"/>
@@ -19259,11 +19441,11 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.929166666666669</v>
+        <v>15.958666666666669</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19271,7 +19453,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.42680314309347978</v>
+        <v>0.4563031430934803</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19377,7 +19559,9 @@
       <c r="AH112" s="56">
         <v>18.266666666666669</v>
       </c>
-      <c r="AI112" s="56"/>
+      <c r="AI112" s="56">
+        <v>17.93333333333333</v>
+      </c>
       <c r="AJ112" s="56"/>
       <c r="AK112" s="56"/>
       <c r="AL112" s="56"/>
@@ -19386,11 +19570,11 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>17.811111111111106</v>
+        <v>17.815999999999995</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19398,7 +19582,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.4314148500090269</v>
+        <v>1.4363037388979158</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19502,7 +19686,9 @@
       <c r="AH113" s="56">
         <v>19.666666666666671</v>
       </c>
-      <c r="AI113" s="56"/>
+      <c r="AI113" s="56">
+        <v>19.733333333333331</v>
+      </c>
       <c r="AJ113" s="56"/>
       <c r="AK113" s="56"/>
       <c r="AL113" s="56"/>
@@ -19511,11 +19697,11 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>19.069565217391304</v>
+        <v>19.097222222222225</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19523,7 +19709,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>0.9451777498347731</v>
+        <v>0.97283475466569413</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19595,7 +19781,9 @@
       <c r="AH114" s="56">
         <v>24.86666666666666</v>
       </c>
-      <c r="AI114" s="56"/>
+      <c r="AI114" s="56">
+        <v>24.13333333333334</v>
+      </c>
       <c r="AJ114" s="56"/>
       <c r="AK114" s="56"/>
       <c r="AL114" s="56"/>
@@ -19604,7 +19792,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -19722,7 +19910,9 @@
       <c r="AH115" s="56">
         <v>27.9</v>
       </c>
-      <c r="AI115" s="56"/>
+      <c r="AI115" s="56">
+        <v>26.25</v>
+      </c>
       <c r="AJ115" s="56"/>
       <c r="AK115" s="56"/>
       <c r="AL115" s="56"/>
@@ -19731,11 +19921,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.215624999999999</v>
+        <v>26.216999999999999</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19743,7 +19933,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.37114502224697787</v>
+        <v>0.37252002224697733</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19974,7 +20164,9 @@
       <c r="AH117" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="AI117" s="56"/>
+      <c r="AI117" s="56">
+        <v>25.533333333333331</v>
+      </c>
       <c r="AJ117" s="56"/>
       <c r="AK117" s="56"/>
       <c r="AL117" s="56"/>
@@ -19983,11 +20175,11 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>26.25833333333334</v>
+        <v>26.22933333333334</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19995,7 +20187,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.88949372759859102</v>
+        <v>0.86049372759859111</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20228,7 +20420,9 @@
       <c r="AH119" s="56">
         <v>23.8</v>
       </c>
-      <c r="AI119" s="56"/>
+      <c r="AI119" s="56">
+        <v>24.6</v>
+      </c>
       <c r="AJ119" s="56"/>
       <c r="AK119" s="56"/>
       <c r="AL119" s="56"/>
@@ -20237,11 +20431,11 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ119" s="71">
         <f t="shared" si="4"/>
-        <v>23.577777777777779</v>
+        <v>23.61866666666667</v>
       </c>
       <c r="AR119" s="71">
         <f>IFERROR(VLOOKUP(A119,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20249,7 +20443,7 @@
       </c>
       <c r="AS119" s="71">
         <f t="shared" si="5"/>
-        <v>1.8493369175627699</v>
+        <v>1.8902258064516602</v>
       </c>
     </row>
     <row r="120" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20535,7 +20729,9 @@
       <c r="AH122" s="56">
         <v>10.866666666666671</v>
       </c>
-      <c r="AI122" s="56"/>
+      <c r="AI122" s="56">
+        <v>12.8</v>
+      </c>
       <c r="AJ122" s="56"/>
       <c r="AK122" s="56"/>
       <c r="AL122" s="56"/>
@@ -20544,11 +20740,11 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.173611111111109</v>
+        <v>12.198666666666666</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20556,7 +20752,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.8708541151408298</v>
+        <v>1.8959096706963869</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20739,7 +20935,9 @@
       <c r="AH124" s="56">
         <v>16.93333333333333</v>
       </c>
-      <c r="AI124" s="56"/>
+      <c r="AI124" s="56">
+        <v>17.333333333333329</v>
+      </c>
       <c r="AJ124" s="56"/>
       <c r="AK124" s="56"/>
       <c r="AL124" s="56"/>
@@ -20748,11 +20946,11 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ124" s="71">
         <f t="shared" si="4"/>
-        <v>15.936231884057973</v>
+        <v>15.994444444444445</v>
       </c>
       <c r="AR124" s="71">
         <f>IFERROR(VLOOKUP(A124,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20760,7 +20958,7 @@
       </c>
       <c r="AS124" s="71">
         <f t="shared" si="5"/>
-        <v>0.88717292451446284</v>
+        <v>0.94538548490093532</v>
       </c>
     </row>
     <row r="125" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20931,7 +21129,9 @@
       <c r="AH126" s="56">
         <v>10.53333333333333</v>
       </c>
-      <c r="AI126" s="56"/>
+      <c r="AI126" s="56">
+        <v>11.53333333333333</v>
+      </c>
       <c r="AJ126" s="56"/>
       <c r="AK126" s="56"/>
       <c r="AL126" s="56"/>
@@ -20940,11 +21140,11 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ126" s="71">
         <f t="shared" si="4"/>
-        <v>11.929411764705879</v>
+        <v>11.907407407407405</v>
       </c>
       <c r="AR126" s="71">
         <f>IFERROR(VLOOKUP(A126,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20952,7 +21152,7 @@
       </c>
       <c r="AS126" s="71">
         <f t="shared" si="5"/>
-        <v>1.2169655486421398</v>
+        <v>1.1949611913436655</v>
       </c>
     </row>
     <row r="127" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21295,7 +21495,9 @@
       <c r="AH130" s="56">
         <v>14.9</v>
       </c>
-      <c r="AI130" s="56"/>
+      <c r="AI130" s="56">
+        <v>15.8</v>
+      </c>
       <c r="AJ130" s="56"/>
       <c r="AK130" s="56"/>
       <c r="AL130" s="56"/>
@@ -21304,11 +21506,11 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ130" s="71">
         <f t="shared" si="4"/>
-        <v>15.863888888888889</v>
+        <v>15.861333333333334</v>
       </c>
       <c r="AR130" s="71">
         <f>IFERROR(VLOOKUP(A130,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21316,7 +21518,7 @@
       </c>
       <c r="AS130" s="71">
         <f t="shared" si="5"/>
-        <v>1.6106465144214397</v>
+        <v>1.6080909588658852</v>
       </c>
     </row>
     <row r="131" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21422,7 +21624,9 @@
       <c r="AH131" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="AI131" s="56"/>
+      <c r="AI131" s="56">
+        <v>18.8</v>
+      </c>
       <c r="AJ131" s="56"/>
       <c r="AK131" s="56"/>
       <c r="AL131" s="56"/>
@@ -21431,11 +21635,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.337500000000002</v>
+        <v>18.356000000000002</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21443,7 +21647,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.5446030010960534</v>
+        <v>1.5631030010960529</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21628,7 +21832,9 @@
       <c r="AH133" s="56">
         <v>12.16666666666667</v>
       </c>
-      <c r="AI133" s="56"/>
+      <c r="AI133" s="56">
+        <v>13.4</v>
+      </c>
       <c r="AJ133" s="56"/>
       <c r="AK133" s="56"/>
       <c r="AL133" s="56"/>
@@ -21637,11 +21843,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>13.918055555555554</v>
+        <v>13.89733333333333</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21649,7 +21855,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.2827157809017145</v>
+        <v>1.2619935586794906</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21752,8 +21958,12 @@
       <c r="AG134" s="56">
         <v>17.866666666666671</v>
       </c>
-      <c r="AH134" s="56"/>
-      <c r="AI134" s="56"/>
+      <c r="AH134" s="56">
+        <v>16.333333333333329</v>
+      </c>
+      <c r="AI134" s="56">
+        <v>17.8</v>
+      </c>
       <c r="AJ134" s="56"/>
       <c r="AK134" s="56"/>
       <c r="AL134" s="56"/>
@@ -21762,11 +21972,11 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>17.959420289855071</v>
+        <v>17.887999999999998</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21774,7 +21984,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.3772414474714019</v>
+        <v>2.3058211576163288</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21880,7 +22090,9 @@
       <c r="AH135" s="56">
         <v>19.350000000000001</v>
       </c>
-      <c r="AI135" s="56"/>
+      <c r="AI135" s="56">
+        <v>22.05</v>
+      </c>
       <c r="AJ135" s="56"/>
       <c r="AK135" s="56"/>
       <c r="AL135" s="56"/>
@@ -21889,11 +22101,11 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>20.639583333333334</v>
+        <v>20.695999999999998</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21901,7 +22113,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>1.9577026959282051</v>
+        <v>2.0141193625948688</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22007,7 +22219,9 @@
       <c r="AH136" s="56">
         <v>10.4</v>
       </c>
-      <c r="AI136" s="56"/>
+      <c r="AI136" s="56">
+        <v>10.53333333333333</v>
+      </c>
       <c r="AJ136" s="56"/>
       <c r="AK136" s="56"/>
       <c r="AL136" s="56"/>
@@ -22016,11 +22230,11 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ136" s="71">
         <f t="shared" si="7"/>
-        <v>11.186111111111108</v>
+        <v>11.159999999999995</v>
       </c>
       <c r="AR136" s="71">
         <f>IFERROR(VLOOKUP(A136,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22028,7 +22242,7 @@
       </c>
       <c r="AS136" s="71">
         <f t="shared" si="8"/>
-        <v>0.32846103695464812</v>
+        <v>0.30234992584353471</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22213,7 +22427,9 @@
       <c r="AH138" s="56">
         <v>20.733333333333331</v>
       </c>
-      <c r="AI138" s="56"/>
+      <c r="AI138" s="56">
+        <v>22.4</v>
+      </c>
       <c r="AJ138" s="56"/>
       <c r="AK138" s="56"/>
       <c r="AL138" s="56"/>
@@ -22222,11 +22438,11 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>22.216666666666669</v>
+        <v>22.224</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22234,7 +22450,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.2064455693182694</v>
+        <v>2.213778902651601</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22467,7 +22683,9 @@
       <c r="AH140" s="56">
         <v>15.75</v>
       </c>
-      <c r="AI140" s="56"/>
+      <c r="AI140" s="56">
+        <v>15.6</v>
+      </c>
       <c r="AJ140" s="56"/>
       <c r="AK140" s="56"/>
       <c r="AL140" s="56"/>
@@ -22476,11 +22694,11 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.479166666666668</v>
+        <v>16.444000000000003</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22488,7 +22706,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.88481609489674717</v>
+        <v>0.84964942823008194</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22594,7 +22812,9 @@
       <c r="AH141" s="56">
         <v>10.93333333333333</v>
       </c>
-      <c r="AI141" s="56"/>
+      <c r="AI141" s="56">
+        <v>12.93333333333333</v>
+      </c>
       <c r="AJ141" s="56"/>
       <c r="AK141" s="56"/>
       <c r="AL141" s="56"/>
@@ -22603,11 +22823,11 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.469444444444447</v>
+        <v>13.448000000000002</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22615,7 +22835,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.4554150476063974</v>
+        <v>1.4339706031619528</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22719,7 +22939,9 @@
       <c r="AH142" s="56">
         <v>10.85</v>
       </c>
-      <c r="AI142" s="56"/>
+      <c r="AI142" s="56">
+        <v>11.15</v>
+      </c>
       <c r="AJ142" s="56"/>
       <c r="AK142" s="56"/>
       <c r="AL142" s="56"/>
@@ -22728,11 +22950,11 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>11.66413043478261</v>
+        <v>11.642708333333333</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22740,7 +22962,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.1351444583008092</v>
+        <v>1.1137223568515324</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22846,7 +23068,9 @@
       <c r="AH143" s="56">
         <v>27.333333333333329</v>
       </c>
-      <c r="AI143" s="56"/>
+      <c r="AI143" s="56">
+        <v>28.533333333333331</v>
+      </c>
       <c r="AJ143" s="56"/>
       <c r="AK143" s="56"/>
       <c r="AL143" s="56"/>
@@ -22855,11 +23079,11 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.62222222222222</v>
+        <v>27.658666666666662</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22867,7 +23091,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>1.7602821300563392</v>
+        <v>1.7967265745007808</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23098,7 +23322,9 @@
       <c r="AH145" s="56">
         <v>20.266666666666669</v>
       </c>
-      <c r="AI145" s="56"/>
+      <c r="AI145" s="56">
+        <v>19.333333333333329</v>
+      </c>
       <c r="AJ145" s="56"/>
       <c r="AK145" s="56"/>
       <c r="AL145" s="56"/>
@@ -23107,11 +23333,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>19.477777777777778</v>
+        <v>19.471999999999998</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23119,7 +23345,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>0.43576124327965715</v>
+        <v>0.42998346550187705</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23222,8 +23448,12 @@
       <c r="AG146" s="56">
         <v>29.13333333333334</v>
       </c>
-      <c r="AH146" s="56"/>
-      <c r="AI146" s="56"/>
+      <c r="AH146" s="56">
+        <v>31</v>
+      </c>
+      <c r="AI146" s="56">
+        <v>29.666666666666671</v>
+      </c>
       <c r="AJ146" s="56"/>
       <c r="AK146" s="56"/>
       <c r="AL146" s="56"/>
@@ -23232,11 +23462,11 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v>29.889855072463764</v>
+        <v>29.925333333333327</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23244,7 +23474,7 @@
       </c>
       <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v>1.132655534666533</v>
+        <v>1.1681337955360966</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23350,7 +23580,9 @@
       <c r="AH147" s="56">
         <v>25.86666666666666</v>
       </c>
-      <c r="AI147" s="56"/>
+      <c r="AI147" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="AJ147" s="56"/>
       <c r="AK147" s="56"/>
       <c r="AL147" s="56"/>
@@ -23359,11 +23591,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.152777777777782</v>
+        <v>25.176000000000002</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23371,7 +23603,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.6487202859144219</v>
+        <v>1.6719425081366417</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23473,7 +23705,9 @@
       <c r="AH148" s="56">
         <v>31.43333333333333</v>
       </c>
-      <c r="AI148" s="56"/>
+      <c r="AI148" s="56">
+        <v>30</v>
+      </c>
       <c r="AJ148" s="56"/>
       <c r="AK148" s="56"/>
       <c r="AL148" s="56"/>
@@ -23482,11 +23716,11 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.34393939393939</v>
+        <v>30.328985507246376</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23494,7 +23728,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.7024081630846091</v>
+        <v>1.6874542763915947</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23600,7 +23834,9 @@
       <c r="AH149" s="56">
         <v>24.266666666666669</v>
       </c>
-      <c r="AI149" s="56"/>
+      <c r="AI149" s="56">
+        <v>23.066666666666659</v>
+      </c>
       <c r="AJ149" s="56"/>
       <c r="AK149" s="56"/>
       <c r="AL149" s="56"/>
@@ -23609,11 +23845,11 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.591666666666669</v>
+        <v>23.570666666666668</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23621,7 +23857,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.7155988937138176</v>
+        <v>1.6945988937138168</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24089,7 +24325,9 @@
       <c r="AH154" s="56">
         <v>19.649999999999999</v>
       </c>
-      <c r="AI154" s="56"/>
+      <c r="AI154" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AJ154" s="56"/>
       <c r="AK154" s="56"/>
       <c r="AL154" s="56"/>
@@ -24098,11 +24336,11 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>20.472916666666666</v>
+        <v>20.462</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24110,7 +24348,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>0.9592959122717275</v>
+        <v>0.94837924560506082</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24216,7 +24454,9 @@
       <c r="AH155" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="AI155" s="56"/>
+      <c r="AI155" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AJ155" s="56"/>
       <c r="AK155" s="56"/>
       <c r="AL155" s="56"/>
@@ -24225,11 +24465,11 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>28.938888888888886</v>
+        <v>28.917333333333332</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24237,7 +24477,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.216102328033088</v>
+        <v>1.1945467724775334</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24414,7 +24654,9 @@
       <c r="AH157" s="56">
         <v>28.266666666666669</v>
       </c>
-      <c r="AI157" s="56"/>
+      <c r="AI157" s="56">
+        <v>30.2</v>
+      </c>
       <c r="AJ157" s="56"/>
       <c r="AK157" s="56"/>
       <c r="AL157" s="56"/>
@@ -24423,11 +24665,11 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ157" s="71">
         <f t="shared" si="7"/>
-        <v>29.370000000000005</v>
+        <v>29.409523809523815</v>
       </c>
       <c r="AR157" s="71">
         <f>IFERROR(VLOOKUP(A157,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24435,7 +24677,7 @@
       </c>
       <c r="AS157" s="71">
         <f t="shared" si="8"/>
-        <v>1.785572503390604</v>
+        <v>1.8250963129144147</v>
       </c>
     </row>
     <row r="158" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24535,7 +24777,9 @@
       <c r="AH158" s="56">
         <v>29.86666666666666</v>
       </c>
-      <c r="AI158" s="56"/>
+      <c r="AI158" s="56">
+        <v>29.86666666666666</v>
+      </c>
       <c r="AJ158" s="56"/>
       <c r="AK158" s="56"/>
       <c r="AL158" s="56"/>
@@ -24544,11 +24788,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>30.047619047619055</v>
+        <v>30.039393939393946</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24556,7 +24800,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>2.0292068805388546</v>
+        <v>2.0209817723137462</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24656,7 +24900,9 @@
       <c r="AH159" s="56">
         <v>20</v>
       </c>
-      <c r="AI159" s="56"/>
+      <c r="AI159" s="56">
+        <v>19.93333333333333</v>
+      </c>
       <c r="AJ159" s="56"/>
       <c r="AK159" s="56"/>
       <c r="AL159" s="56"/>
@@ -24665,11 +24911,11 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.371428571428574</v>
+        <v>20.351515151515152</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24677,7 +24923,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.3804914567381736</v>
+        <v>1.3605780368247515</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24781,7 +25027,9 @@
         <v>25.6</v>
       </c>
       <c r="AH160" s="56"/>
-      <c r="AI160" s="56"/>
+      <c r="AI160" s="56">
+        <v>27.333333333333329</v>
+      </c>
       <c r="AJ160" s="56"/>
       <c r="AK160" s="56"/>
       <c r="AL160" s="56"/>
@@ -24790,11 +25038,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.017391304347836</v>
+        <v>27.030555555555566</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25015,7 +25263,9 @@
       <c r="AH162" s="56">
         <v>28.666666666666671</v>
       </c>
-      <c r="AI162" s="56"/>
+      <c r="AI162" s="56">
+        <v>29.333333333333329</v>
+      </c>
       <c r="AJ162" s="56"/>
       <c r="AK162" s="56"/>
       <c r="AL162" s="56"/>
@@ -25024,11 +25274,11 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>28.925000000000008</v>
+        <v>28.94133333333334</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25036,7 +25286,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.35146261212572938</v>
+        <v>0.36779594545906136</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25142,7 +25392,9 @@
       <c r="AH163" s="56">
         <v>21.466666666666669</v>
       </c>
-      <c r="AI163" s="56"/>
+      <c r="AI163" s="56">
+        <v>20.733333333333331</v>
+      </c>
       <c r="AJ163" s="56"/>
       <c r="AK163" s="56"/>
       <c r="AL163" s="56"/>
@@ -25151,11 +25403,11 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.433333333333334</v>
+        <v>21.405333333333331</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25163,7 +25415,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.18390951773275432</v>
+        <v>0.15590951773275208</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25267,9 +25519,11 @@
         <v>25.15</v>
       </c>
       <c r="AH164" s="56">
-        <v>25.2</v>
-      </c>
-      <c r="AI164" s="56"/>
+        <v>25.25</v>
+      </c>
+      <c r="AI164" s="56">
+        <v>25.35</v>
+      </c>
       <c r="AJ164" s="56"/>
       <c r="AK164" s="56"/>
       <c r="AL164" s="56"/>
@@ -25278,11 +25532,11 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.397916666666671</v>
+        <v>25.398000000000003</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25290,7 +25544,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.5999890575065905</v>
+        <v>1.600072390839923</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25471,7 +25725,9 @@
       <c r="AH166" s="56">
         <v>14.33333333333333</v>
       </c>
-      <c r="AI166" s="56"/>
+      <c r="AI166" s="56">
+        <v>14.733333333333331</v>
+      </c>
       <c r="AJ166" s="56"/>
       <c r="AK166" s="56"/>
       <c r="AL166" s="56"/>
@@ -25480,11 +25736,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.875757575757577</v>
+        <v>14.869565217391306</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25492,7 +25748,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.2772880417074362</v>
+        <v>1.2710956833411657</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25594,7 +25850,9 @@
       <c r="AH167" s="56">
         <v>20.2</v>
       </c>
-      <c r="AI167" s="56"/>
+      <c r="AI167" s="56">
+        <v>21.06666666666667</v>
+      </c>
       <c r="AJ167" s="56"/>
       <c r="AK167" s="56"/>
       <c r="AL167" s="56"/>
@@ -25603,11 +25861,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.65757575757576</v>
+        <v>20.67536231884058</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25615,7 +25873,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.6220079479651197</v>
+        <v>1.6397945092299402</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25717,7 +25975,9 @@
       <c r="AH168" s="56">
         <v>27.85</v>
       </c>
-      <c r="AI168" s="56"/>
+      <c r="AI168" s="56">
+        <v>28.85</v>
+      </c>
       <c r="AJ168" s="56"/>
       <c r="AK168" s="56"/>
       <c r="AL168" s="56"/>
@@ -25726,11 +25986,11 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.813636363636366</v>
+        <v>27.858695652173918</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25738,7 +25998,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.7477718975697876</v>
+        <v>1.7928311861073389</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25844,7 +26104,9 @@
       <c r="AH169" s="56">
         <v>7.9</v>
       </c>
-      <c r="AI169" s="56"/>
+      <c r="AI169" s="56">
+        <v>9.4499999999999993</v>
+      </c>
       <c r="AJ169" s="56"/>
       <c r="AK169" s="56"/>
       <c r="AL169" s="56"/>
@@ -25853,11 +26115,11 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>8.9458333333333329</v>
+        <v>8.9659999999999993</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25865,7 +26127,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.40370905197879559</v>
+        <v>0.42387571864546203</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25955,7 +26217,9 @@
       <c r="AH170" s="56">
         <v>26.333333333333329</v>
       </c>
-      <c r="AI170" s="56"/>
+      <c r="AI170" s="56">
+        <v>26.466666666666669</v>
+      </c>
       <c r="AJ170" s="56"/>
       <c r="AK170" s="56"/>
       <c r="AL170" s="56"/>
@@ -25964,11 +26228,11 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v>24.745833333333334</v>
+        <v>24.847058823529409</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25976,7 +26240,7 @@
       </c>
       <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v>0.6552093914708621</v>
+        <v>0.75643488166693729</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26080,7 +26344,9 @@
       <c r="AH171" s="56">
         <v>21.133333333333329</v>
       </c>
-      <c r="AI171" s="56"/>
+      <c r="AI171" s="56">
+        <v>19.866666666666671</v>
+      </c>
       <c r="AJ171" s="56"/>
       <c r="AK171" s="56"/>
       <c r="AL171" s="56"/>
@@ -26089,11 +26355,11 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>20.834782608695654</v>
+        <v>20.794444444444448</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26101,7 +26367,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.9058565864437362</v>
+        <v>1.8655184221925296</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26203,7 +26469,9 @@
       <c r="AH172" s="56">
         <v>26.75</v>
       </c>
-      <c r="AI172" s="56"/>
+      <c r="AI172" s="56">
+        <v>25.55</v>
+      </c>
       <c r="AJ172" s="56"/>
       <c r="AK172" s="56"/>
       <c r="AL172" s="56"/>
@@ -26212,11 +26480,11 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.679545454545458</v>
+        <v>25.673913043478262</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26224,7 +26492,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.2409170860335799</v>
+        <v>1.2352846749663833</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26330,7 +26598,9 @@
       <c r="AH173" s="56">
         <v>25.45</v>
       </c>
-      <c r="AI173" s="56"/>
+      <c r="AI173" s="56">
+        <v>24.65</v>
+      </c>
       <c r="AJ173" s="56"/>
       <c r="AK173" s="56"/>
       <c r="AL173" s="56"/>
@@ -26339,11 +26609,11 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.144097222222229</v>
+        <v>25.12433333333334</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26351,7 +26621,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.0896886200716978</v>
+        <v>1.0699247311828088</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26455,7 +26725,9 @@
       <c r="AH174" s="56">
         <v>13.6</v>
       </c>
-      <c r="AI174" s="56"/>
+      <c r="AI174" s="56">
+        <v>14.4</v>
+      </c>
       <c r="AJ174" s="56"/>
       <c r="AK174" s="56"/>
       <c r="AL174" s="56"/>
@@ -26464,11 +26736,11 @@
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ174" s="71">
         <f t="shared" si="7"/>
-        <v>13.828985507246381</v>
+        <v>13.852777777777781</v>
       </c>
       <c r="AR174" s="71">
         <f>IFERROR(VLOOKUP(A174,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26476,7 +26748,7 @@
       </c>
       <c r="AS174" s="71">
         <f t="shared" si="8"/>
-        <v>1.7682336495745208</v>
+        <v>1.792025920105921</v>
       </c>
     </row>
     <row r="175" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26851,7 +27123,9 @@
       <c r="AH178" s="56">
         <v>25.133333333333329</v>
       </c>
-      <c r="AI178" s="56"/>
+      <c r="AI178" s="56">
+        <v>23.86666666666666</v>
+      </c>
       <c r="AJ178" s="56"/>
       <c r="AK178" s="56"/>
       <c r="AL178" s="56"/>
@@ -26860,11 +27134,11 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>25.214035087719296</v>
+        <v>25.146666666666665</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26872,7 +27146,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.66175474084040431</v>
+        <v>0.59438631978777323</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26970,7 +27244,9 @@
       <c r="AH179" s="56">
         <v>17.7</v>
       </c>
-      <c r="AI179" s="56"/>
+      <c r="AI179" s="56">
+        <v>18.45</v>
+      </c>
       <c r="AJ179" s="56"/>
       <c r="AK179" s="56"/>
       <c r="AL179" s="56"/>
@@ -26979,11 +27255,11 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>18.625</v>
+        <v>18.616666666666667</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26991,7 +27267,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>1.0374163164833483</v>
+        <v>1.0290829831500155</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27176,7 +27452,9 @@
       <c r="AH181" s="56">
         <v>31.333333333333329</v>
       </c>
-      <c r="AI181" s="56"/>
+      <c r="AI181" s="56">
+        <v>30.466666666666669</v>
+      </c>
       <c r="AJ181" s="56"/>
       <c r="AK181" s="56"/>
       <c r="AL181" s="56"/>
@@ -27185,11 +27463,11 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ181" s="71">
         <f t="shared" si="7"/>
-        <v>30.924999999999997</v>
+        <v>30.906666666666666</v>
       </c>
       <c r="AR181" s="71">
         <f>IFERROR(VLOOKUP(A181,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27197,7 +27475,7 @@
       </c>
       <c r="AS181" s="71">
         <f t="shared" si="8"/>
-        <v>2.3917636124301858</v>
+        <v>2.3734302790968549</v>
       </c>
     </row>
     <row r="182" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27461,7 +27739,9 @@
       <c r="AH184" s="56">
         <v>29.2</v>
       </c>
-      <c r="AI184" s="56"/>
+      <c r="AI184" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AJ184" s="56"/>
       <c r="AK184" s="56"/>
       <c r="AL184" s="56"/>
@@ -27470,11 +27750,11 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>28.138888888888889</v>
+        <v>28.101333333333336</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27482,7 +27762,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.5005176712719006</v>
+        <v>1.4629621157163477</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27865,7 +28145,9 @@
       <c r="AH188" s="56">
         <v>17.06666666666667</v>
       </c>
-      <c r="AI188" s="56"/>
+      <c r="AI188" s="56">
+        <v>16.8</v>
+      </c>
       <c r="AJ188" s="56"/>
       <c r="AK188" s="56"/>
       <c r="AL188" s="56"/>
@@ -27874,11 +28156,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>17.383333333333336</v>
+        <v>17.360000000000003</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27886,7 +28168,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.387741343801606</v>
+        <v>1.3644080104682725</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27980,7 +28262,9 @@
       <c r="AH189" s="56">
         <v>31.466666666666669</v>
       </c>
-      <c r="AI189" s="56"/>
+      <c r="AI189" s="56">
+        <v>31.86666666666666</v>
+      </c>
       <c r="AJ189" s="56"/>
       <c r="AK189" s="56"/>
       <c r="AL189" s="56"/>
@@ -27989,11 +28273,11 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>32.033333333333339</v>
+        <v>32.024561403508777</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28001,7 +28285,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>2.1817489752805486</v>
+        <v>2.1729770454559869</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28107,7 +28391,9 @@
       <c r="AH190" s="56">
         <v>30.93333333333333</v>
       </c>
-      <c r="AI190" s="56"/>
+      <c r="AI190" s="56">
+        <v>30.4</v>
+      </c>
       <c r="AJ190" s="56"/>
       <c r="AK190" s="56"/>
       <c r="AL190" s="56"/>
@@ -28116,11 +28402,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>30.619444444444444</v>
+        <v>30.610666666666667</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28128,7 +28414,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.702920782961975</v>
+        <v>1.6941430051841984</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28234,7 +28520,9 @@
       <c r="AH191" s="56">
         <v>18.25</v>
       </c>
-      <c r="AI191" s="56"/>
+      <c r="AI191" s="56">
+        <v>18.25</v>
+      </c>
       <c r="AJ191" s="56"/>
       <c r="AK191" s="56"/>
       <c r="AL191" s="56"/>
@@ -28243,11 +28531,11 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.664583333333329</v>
+        <v>18.647999999999996</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28255,7 +28543,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.2773643186727206</v>
+        <v>1.2607809853393874</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28361,7 +28649,9 @@
       <c r="AH192" s="56">
         <v>27.06666666666667</v>
       </c>
-      <c r="AI192" s="56"/>
+      <c r="AI192" s="56">
+        <v>26</v>
+      </c>
       <c r="AJ192" s="56"/>
       <c r="AK192" s="56"/>
       <c r="AL192" s="56"/>
@@ -28370,11 +28660,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.155555555555566</v>
+        <v>26.149333333333342</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28382,7 +28672,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.91104837473739408</v>
+        <v>0.90482615251517018</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28482,7 +28772,9 @@
       <c r="AH193" s="56">
         <v>28.5</v>
       </c>
-      <c r="AI193" s="56"/>
+      <c r="AI193" s="56">
+        <v>26.7</v>
+      </c>
       <c r="AJ193" s="56"/>
       <c r="AK193" s="56"/>
       <c r="AL193" s="56"/>
@@ -28491,11 +28783,11 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>27.104761904761901</v>
+        <v>27.086363636363636</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28503,7 +28795,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>0.75199236475273068</v>
+        <v>0.73359409635446582</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28609,7 +28901,9 @@
       <c r="AH194" s="56">
         <v>21.733333333333331</v>
       </c>
-      <c r="AI194" s="56"/>
+      <c r="AI194" s="56">
+        <v>20.733333333333331</v>
+      </c>
       <c r="AJ194" s="56"/>
       <c r="AK194" s="56"/>
       <c r="AL194" s="56"/>
@@ -28618,11 +28912,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.238888888888891</v>
+        <v>21.218666666666667</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28630,7 +28924,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-0.36877290816953945</v>
+        <v>-0.3889951303917627</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28736,7 +29030,9 @@
       <c r="AH195" s="56">
         <v>26.6</v>
       </c>
-      <c r="AI195" s="56"/>
+      <c r="AI195" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AJ195" s="56"/>
       <c r="AK195" s="56"/>
       <c r="AL195" s="56"/>
@@ -28745,11 +29041,11 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>27.755555555555556</v>
+        <v>27.693333333333335</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28757,7 +29053,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>2.0680673458457974</v>
+        <v>2.0058451236235761</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28863,7 +29159,9 @@
       <c r="AH196" s="56">
         <v>20.6</v>
       </c>
-      <c r="AI196" s="56"/>
+      <c r="AI196" s="56">
+        <v>21.733333333333331</v>
+      </c>
       <c r="AJ196" s="56"/>
       <c r="AK196" s="56"/>
       <c r="AL196" s="56"/>
@@ -28872,11 +29170,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>22.180555555555557</v>
+        <v>22.16266666666667</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28884,7 +29182,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>1.9567990840302869</v>
+        <v>1.9389101951413998</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28998,11 +29296,11 @@
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
-        <f t="shared" ref="AP197:AP212" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
+        <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
         <v>24</v>
       </c>
       <c r="AQ197" s="71">
-        <f t="shared" ref="AQ197:AQ212" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
+        <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
         <v>25.877777777777776</v>
       </c>
       <c r="AR197" s="71">
@@ -29010,7 +29308,7 @@
         <v>24.127383001170529</v>
       </c>
       <c r="AS197" s="71">
-        <f t="shared" ref="AS197:AS212" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
+        <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
         <v>1.7503947766072478</v>
       </c>
     </row>
